--- a/data/C_1000_6000K.xlsx
+++ b/data/C_1000_6000K.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\CC_scripts\Shermo_post\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrc\Desktop\ThermoCR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE66B3F-BE80-4026-9422-B683494D7F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE55BE19-872A-427C-8724-924B394E9B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -299,7 +288,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T(K)</t>
+    <t>T/K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -666,9 +655,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="33" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -697,7 +686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1000</v>
       </c>
@@ -727,7 +716,7 @@
         <v>158.82100000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1100</v>
       </c>
@@ -757,7 +746,7 @@
         <v>158.71181818181816</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1200</v>
       </c>
@@ -787,7 +776,7 @@
         <v>158.56249999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1300</v>
       </c>
@@ -817,7 +806,7 @@
         <v>158.3861538461538</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1400</v>
       </c>
@@ -847,7 +836,7 @@
         <v>158.19428571428566</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1500</v>
       </c>
@@ -877,7 +866,7 @@
         <v>157.99199999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>1600</v>
       </c>
@@ -907,7 +896,7 @@
         <v>157.78312499999998</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1700</v>
       </c>
@@ -937,7 +926,7 @@
         <v>157.57235294117652</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1800</v>
       </c>
@@ -967,7 +956,7 @@
         <v>157.36055555555555</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1900</v>
       </c>
@@ -997,7 +986,7 @@
         <v>157.15000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>2000</v>
       </c>
@@ -1027,7 +1016,7 @@
         <v>156.94149999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>2100</v>
       </c>
@@ -1057,7 +1046,7 @@
         <v>156.73619047619044</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2200</v>
       </c>
@@ -1087,7 +1076,7 @@
         <v>156.53409090909091</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2300</v>
       </c>
@@ -1117,7 +1106,7 @@
         <v>156.33652173913046</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2400</v>
       </c>
@@ -1147,7 +1136,7 @@
         <v>156.14250000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>2500</v>
       </c>
@@ -1177,7 +1166,7 @@
         <v>155.95320000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2600</v>
       </c>
@@ -1207,7 +1196,7 @@
         <v>155.76769230769233</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>2700</v>
       </c>
@@ -1237,7 +1226,7 @@
         <v>155.58666666666664</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2800</v>
       </c>
@@ -1267,7 +1256,7 @@
         <v>155.41035714285712</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2900</v>
       </c>
@@ -1297,7 +1286,7 @@
         <v>155.23793103448276</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>3000</v>
       </c>
@@ -1327,7 +1316,7 @@
         <v>155.06966666666668</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>3100</v>
       </c>
@@ -1357,7 +1346,7 @@
         <v>154.90548387096777</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>3200</v>
       </c>
@@ -1387,7 +1376,7 @@
         <v>154.7446875</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>3300</v>
       </c>
@@ -1417,7 +1406,7 @@
         <v>154.58757575757576</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>3400</v>
       </c>
@@ -1447,7 +1436,7 @@
         <v>154.43382352941177</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>3500</v>
       </c>
@@ -1477,7 +1466,7 @@
         <v>154.28314285714285</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>3600</v>
       </c>
@@ -1507,7 +1496,7 @@
         <v>154.13583333333332</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>3700</v>
       </c>
@@ -1537,7 +1526,7 @@
         <v>153.99135135135131</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>3800</v>
       </c>
@@ -1567,7 +1556,7 @@
         <v>153.84947368421052</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>3900</v>
       </c>
@@ -1597,7 +1586,7 @@
         <v>153.71</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>4000</v>
       </c>
@@ -1627,7 +1616,7 @@
         <v>153.57300000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>4100</v>
       </c>
@@ -1657,7 +1646,7 @@
         <v>153.4380487804878</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>4200</v>
       </c>
@@ -1687,7 +1676,7 @@
         <v>153.30500000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>4300</v>
       </c>
@@ -1717,7 +1706,7 @@
         <v>153.17418604651166</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>4400</v>
       </c>
@@ -1747,7 +1736,7 @@
         <v>153.04499999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>4500</v>
       </c>
@@ -1777,7 +1766,7 @@
         <v>152.91755555555557</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>4600</v>
       </c>
@@ -1807,7 +1796,7 @@
         <v>152.79173913043482</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>4700</v>
       </c>
@@ -1837,7 +1826,7 @@
         <v>152.66723404255319</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>4800</v>
       </c>
@@ -1867,7 +1856,7 @@
         <v>152.54395833333334</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>4900</v>
       </c>
@@ -1897,7 +1886,7 @@
         <v>152.4220408163265</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>5000</v>
       </c>
@@ -1927,7 +1916,7 @@
         <v>152.30119999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>5100</v>
       </c>
@@ -1957,7 +1946,7 @@
         <v>152.18137254901961</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>5200</v>
       </c>
@@ -1987,7 +1976,7 @@
         <v>152.06269230769232</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>5300</v>
       </c>
@@ -2017,7 +2006,7 @@
         <v>151.94471698113207</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>5400</v>
       </c>
@@ -2047,7 +2036,7 @@
         <v>151.82777777777778</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>5500</v>
       </c>
@@ -2077,7 +2066,7 @@
         <v>151.71145454545456</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>5600</v>
       </c>
@@ -2107,7 +2096,7 @@
         <v>151.59589285714284</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>5700</v>
       </c>
@@ -2137,7 +2126,7 @@
         <v>151.48122807017543</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>5800</v>
       </c>
@@ -2167,7 +2156,7 @@
         <v>151.36706896551723</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>5900</v>
       </c>
@@ -2197,7 +2186,7 @@
         <v>151.25355932203391</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>6000</v>
       </c>
